--- a/etf_holdings/2026-10-29_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-29_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-29 00:03:02</t>
+          <t>2026-10-29 23:20:09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+1.04%2425</t>
+          <t>-0.41%2415</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+1.04%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2425</v>
+        <v>2415</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>14.17%7,700,000</t>
+          <t>14.48%7,700,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>14.17%</t>
+          <t>14.48%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-29 00:03:02</t>
+          <t>2026-10-29 23:20:09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+3.77%1100</t>
+          <t>-5.45%1040</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+3.77%</t>
+          <t>-5.45%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1100</v>
+        <v>1040</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.01%7,200,000</t>
+          <t>5.83%7,200,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.01%</t>
+          <t>5.83%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29 00:03:02</t>
+          <t>2026-10-29 23:20:09</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+2.72%3215</t>
+          <t>-3.42%3105</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+2.72%</t>
+          <t>-3.42%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3215</v>
+        <v>3105</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5.69%2,330,000</t>
+          <t>5.63%2,330,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.69%</t>
+          <t>5.63%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-29 00:03:02</t>
+          <t>2026-10-29 23:20:09</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -687,38 +687,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+6.94%4235</t>
+          <t>+0.47%6405</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+6.94%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>4235</v>
+        <v>6405</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4.92%1,530,000</t>
+          <t>4.99%1,000,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>4.92%</t>
+          <t>4.99%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>1530000</v>
+        <v>1000000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-29 00:03:02</t>
+          <t>2026-10-29 23:20:09</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,38 +748,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+8.79%6375</t>
+          <t>-4.49%4045</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+8.79%</t>
+          <t>-4.49%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>6375</v>
+        <v>4045</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4.84%1,000,000</t>
+          <t>4.82%1,530,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4.84%</t>
+          <t>4.82%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1000000</v>
+        <v>1530000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-29 00:03:02</t>
+          <t>2026-10-29 23:20:09</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+5.79%5025</t>
+          <t>-0.3%5010</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+5.79%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>5025</v>
+        <v>5010</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.58%1,200,000</t>
+          <t>4.68%1,200,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.58%</t>
+          <t>4.68%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-29 00:03:02</t>
+          <t>2026-10-29 23:20:09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+9.96%8170</t>
+          <t>-6.49%7640</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+9.96%</t>
+          <t>-6.49%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>8170</v>
+        <v>7640</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.40%710,000</t>
+          <t>4.22%710,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.40%</t>
+          <t>4.22%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-29 00:03:02</t>
+          <t>2026-10-29 23:20:09</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+4.99%547</t>
+          <t>-0.73%543</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+4.99%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.65%8,800,000</t>
+          <t>3.72%8,800,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.65%</t>
+          <t>3.72%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-29 00:03:02</t>
+          <t>2026-10-29 23:20:09</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+6.78%5115</t>
+          <t>-5.38%4840</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+6.78%</t>
+          <t>-5.38%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5115</v>
+        <v>4840</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.61%930,000</t>
+          <t>3.50%930,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.61%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-29 00:03:02</t>
+          <t>2026-10-29 23:20:09</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+9.99%1035</t>
+          <t>-7.34%959</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+9.99%</t>
+          <t>-7.34%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1035</v>
+        <v>959</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.50%4,450,000</t>
+          <t>3.32%4,450,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>3.32%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>-0.26%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-29 00:03:02</t>
+          <t>2026-10-29 23:20:09</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+2.65%1550</t>
+          <t>-3.85%1250</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+2.65%</t>
+          <t>-3.85%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1550</v>
+        <v>1250</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.13%2,658,000</t>
+          <t>2.93%3,010,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.13%</t>
+          <t>2.93%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>2658000</v>
+        <v>3010000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-29 00:03:02</t>
+          <t>2026-10-29 23:20:09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>1303南亞</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+3.59%1300</t>
+          <t>-2.19%312</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+3.59%</t>
+          <t>-2.19%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1300</v>
+        <v>312</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.97%3,010,000</t>
+          <t>2.91%12,000,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.97%</t>
+          <t>2.91%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>3010000</v>
+        <v>12000000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-29 00:03:02</t>
+          <t>2026-10-29 23:20:09</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1303南亞</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+7.23%319</t>
+          <t>-4.52%1480</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+7.23%</t>
+          <t>-4.52%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>319</v>
+        <v>1480</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.91%12,000,000</t>
+          <t>2.76%2,393,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.91%</t>
+          <t>2.76%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>12000000</v>
+        <v>2393000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-29 00:03:02</t>
+          <t>2026-10-29 23:20:09</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,25 +1302,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0%1950</t>
+          <t>-3.33%1885</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-3.33%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1950</v>
+        <v>1885</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.74%1,850,956</t>
+          <t>2.72%1,850,956</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>2.72%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-29 00:03:02</t>
+          <t>2026-10-29 23:20:09</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,25 +1363,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+7.42%1375</t>
+          <t>+1.09%1390</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+7.42%</t>
+          <t>+1.09%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1375</v>
+        <v>1390</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.51%2,400,000</t>
+          <t>2.60%2,400,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.51%</t>
+          <t>2.60%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-29 00:03:04</t>
+          <t>2026-10-29 23:20:10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+8.19%1585</t>
+          <t>-1.82%16980</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+8.19%</t>
+          <t>-1.82%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1585</v>
+        <v>16980</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.26%1,880,000</t>
+          <t>2.39%180,500</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>2.39%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>1880000</v>
+        <v>180500</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-29 00:03:04</t>
+          <t>2026-10-29 23:20:10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+7.99%17295</t>
+          <t>-2.52%1545</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+7.99%</t>
+          <t>-2.52%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>17295</v>
+        <v>1545</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.24%170,500</t>
+          <t>2.26%1,880,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.24%</t>
+          <t>2.26%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>170500</v>
+        <v>1880000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-29 00:03:04</t>
+          <t>2026-10-29 23:20:10</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,25 +1546,25 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+3.13%1815</t>
+          <t>-3.31%1755</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+3.13%</t>
+          <t>-3.31%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1815</v>
+        <v>1755</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.20%1,600,000</t>
+          <t>2.19%1,600,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.20%</t>
+          <t>2.19%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-29 00:03:04</t>
+          <t>2026-10-29 23:20:10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,25 +1607,25 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+4.32%1810</t>
+          <t>-5.8%1705</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+4.32%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1810</v>
+        <v>1705</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.01%1,460,000</t>
+          <t>1.94%1,460,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>1.94%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-29 00:03:04</t>
+          <t>2026-10-29 23:20:10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,25 +1668,25 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+5.58%6335</t>
+          <t>-8.21%5815</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+5.58%</t>
+          <t>-8.21%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>6335</v>
+        <v>5815</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.80%375,000</t>
+          <t>1.70%375,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.70%</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-29 00:03:04</t>
+          <t>2026-10-29 23:20:10</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+8.16%477</t>
+          <t>0%477</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+8.16%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -1742,12 +1742,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.01%2,800,000</t>
+          <t>1.04%2,800,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>1.04%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-29 00:03:04</t>
+          <t>2026-10-29 23:20:10</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,16 +1790,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+3.16%277.5</t>
+          <t>-2.88%269.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+3.16%</t>
+          <t>-2.88%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>277.5</v>
+        <v>269.5</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-29 00:03:04</t>
+          <t>2026-10-29 23:20:10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,33 +1851,33 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+9.72%1185</t>
+          <t>-5.91%1115</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+9.72%</t>
+          <t>-5.91%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1185</v>
+        <v>1115</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.74%820,000</t>
+          <t>0.81%930,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.74%</t>
+          <t>0.81%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>820000</v>
+        <v>930000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-29 00:03:04</t>
+          <t>2026-10-29 23:20:10</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,16 +1912,16 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+3.47%10150</t>
+          <t>-2.66%9880</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+3.47%</t>
+          <t>-2.66%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>10150</v>
+        <v>9880</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-29 00:03:04</t>
+          <t>2026-10-29 23:20:10</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2317鴻海</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+1.62%251.5</t>
+          <t>-1.73%683</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+1.62%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>251.5</v>
+        <v>683</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.61%3,200,000</t>
+          <t>0.69%1,300,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>0.69%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>3200000</v>
+        <v>1300000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-29 00:03:04</t>
+          <t>2026-10-29 23:20:10</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>6805富世達</t>
+          <t>2317鴻海</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+9.33%2460</t>
+          <t>-1.39%248</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+9.33%</t>
+          <t>-1.39%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>2460</v>
+        <v>248</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.58%310,000</t>
+          <t>0.62%3,200,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>310000</v>
+        <v>3200000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-29 00:03:04</t>
+          <t>2026-10-29 23:20:10</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>6805富世達</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+4.49%128</t>
+          <t>-1.42%2425</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+4.49%</t>
+          <t>-1.42%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>128</v>
+        <v>2425</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.58%6,000,000</t>
+          <t>0.59%310,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.59%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>6000000</v>
+        <v>310000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-29 00:03:04</t>
+          <t>2026-10-29 23:20:10</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,25 +2151,25 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3211順達</t>
+          <t>3450聯鈞</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+3.06%337</t>
+          <t>-1.93%433</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+3.06%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>337</v>
+        <v>433</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.51%2,000,000</t>
+          <t>0.51%1,500,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2178,11 +2178,11 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-29 00:03:04</t>
+          <t>2026-10-29 23:20:10</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,25 +2212,25 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3450聯鈞</t>
+          <t>3211順達</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+2.91%441.5</t>
+          <t>-4.15%323</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+2.91%</t>
+          <t>-4.15%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>441.5</v>
+        <v>323</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.50%1,500,000</t>
+          <t>0.50%2,000,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2239,11 +2239,11 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>1500000</v>
+        <v>2000000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-29 00:03:04</t>
+          <t>2026-10-29 23:20:10</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>1560中砂</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+6.76%695</t>
+          <t>-2.84%888</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+6.76%</t>
+          <t>-2.84%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>695</v>
+        <v>888</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.47%900,000</t>
+          <t>0.38%550,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>900000</v>
+        <v>550000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-29 00:03:05</t>
+          <t>2026-10-29 23:20:12</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1560中砂</t>
+          <t>6442光聖</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+9.86%914</t>
+          <t>-7.12%1305</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+9.86%</t>
+          <t>-7.12%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>914</v>
+        <v>1305</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.38%550,000</t>
+          <t>0.36%350,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>550000</v>
+        <v>350000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-29 00:03:05</t>
+          <t>2026-10-29 23:20:12</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>6442光聖</t>
+          <t>2882國泰金</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+1.81%1405</t>
+          <t>+0.87%116.5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+1.81%</t>
+          <t>+0.87%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1405</v>
+        <v>116.5</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.37%350,000</t>
+          <t>0.36%4,000,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>350000</v>
+        <v>4000000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-29 00:03:05</t>
+          <t>2026-10-29 23:20:12</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2882國泰金</t>
+          <t>2313華通</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+1.32%115.5</t>
+          <t>-4.69%213.5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+1.32%</t>
+          <t>-4.69%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>115.5</v>
+        <v>213.5</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.35%4,000,000</t>
+          <t>0.33%2,000,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.33%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>4000000</v>
+        <v>2000000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-29 00:03:05</t>
+          <t>2026-10-29 23:20:12</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2313華通</t>
+          <t>3583辛耘</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+3.7%224</t>
+          <t>-2.93%597</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+3.7%</t>
+          <t>-2.93%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>224</v>
+        <v>597</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.34%2,000,000</t>
+          <t>0.30%650,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>2000000</v>
+        <v>650000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-29 00:03:05</t>
+          <t>2026-10-29 23:20:12</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,38 +2578,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>3583辛耘</t>
+          <t>6488環球晶</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+3.89%615</t>
+          <t>-4.12%814</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+3.89%</t>
+          <t>-4.12%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>615</v>
+        <v>814</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.34%723,000</t>
+          <t>0.19%300,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.19%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>723000</v>
+        <v>300000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-29 00:03:05</t>
+          <t>2026-10-29 23:20:12</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,38 +2639,38 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>6488環球晶</t>
+          <t>2883凱基金</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+4.3%849</t>
+          <t>-0.13%38.5</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+4.3%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>849</v>
+        <v>38.5</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.19%300,000</t>
+          <t>0.12%4,000,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.12%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>300000</v>
+        <v>4000000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-29 00:03:05</t>
+          <t>2026-10-29 23:20:12</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,38 +2700,38 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2883凱基金</t>
+          <t>2455全新</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+0.26%38.55</t>
+          <t>-5.47%484</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>-5.47%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>38.55</v>
+        <v>484</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.12%4,000,000</t>
+          <t>0.08%200,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>0.08%</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>4000000</v>
+        <v>200000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-29 00:03:05</t>
+          <t>2026-10-29 23:20:12</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,38 +2761,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2455全新</t>
+          <t>6285啟碁</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+9.87%512</t>
+          <t>-3.81%227.5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+9.87%</t>
+          <t>-3.81%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>512</v>
+        <v>227.5</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.08%200,000</t>
+          <t>0.06%350,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.08%</t>
+          <t>0.06%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>200000</v>
+        <v>350000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-29 00:03:05</t>
+          <t>2026-10-29 23:20:12</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,25 +2822,25 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>6285啟碁</t>
+          <t>2301光寶科</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+3.73%236.5</t>
+          <t>-3.63%252</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+3.73%</t>
+          <t>-3.63%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>236.5</v>
+        <v>252</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.06%350,000</t>
+          <t>0.06%300,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2849,11 +2849,11 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>350000</v>
+        <v>300000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-29 00:03:05</t>
+          <t>2026-10-29 23:20:12</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,38 +2883,38 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2301光寶科</t>
+          <t>1717長興</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+3.56%261.5</t>
+          <t>-2.41%68.7</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+3.56%</t>
+          <t>-2.41%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>261.5</v>
+        <v>68.7</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.06%300,000</t>
+          <t>0.05%900,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.06%</t>
+          <t>0.05%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>300000</v>
+        <v>900000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-29 00:03:05</t>
+          <t>2026-10-29 23:20:12</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,38 +2944,38 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1717長興</t>
+          <t>2481強茂</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+2.62%70.4</t>
+          <t>-4.5%148.5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+2.62%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>70.40000000000001</v>
+        <v>148.5</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.05%900,000</t>
+          <t>0.04%350,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0.04%</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>900000</v>
+        <v>350000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-29 00:03:05</t>
+          <t>2026-10-29 23:20:12</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,34 +3005,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2481強茂</t>
+          <t>3264欣銓</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+3.67%155.5</t>
+          <t>-0.42%236.5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+3.67%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>155.5</v>
+        <v>236.5</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.04%350,000</t>
+          <t>0%1,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>350000</v>
+        <v>1000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-29 00:03:05</t>
+          <t>2026-10-29 23:20:12</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,21 +3066,21 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>3264欣銓</t>
+          <t>8358金居</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-4.23%237.5</t>
+          <t>-4.67%438.5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-4.23%</t>
+          <t>-4.67%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>237.5</v>
+        <v>438.5</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-29 00:03:05</t>
+          <t>2026-10-29 23:20:12</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,21 +3127,21 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>8358金居</t>
+          <t>8299群聯</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+9.39%460</t>
+          <t>+0.49%2050</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+9.39%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>460</v>
+        <v>2050</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-29 00:03:05</t>
+          <t>2026-10-29 23:20:12</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,21 +3188,21 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>8299群聯</t>
+          <t>6196帆宣</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+6.81%2040</t>
+          <t>-4.22%567</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+6.81%</t>
+          <t>-4.22%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>2040</v>
+        <v>567</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-29 00:03:06</t>
+          <t>2026-10-29 23:20:13</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3249,21 +3249,21 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>6196帆宣</t>
+          <t>6239力成</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+1.37%592</t>
+          <t>-0.73%270.5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+1.37%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>592</v>
+        <v>270.5</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-29 00:03:06</t>
+          <t>2026-10-29 23:20:13</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3310,21 +3310,21 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>6239力成</t>
+          <t>2049上銀</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+7.07%272.5</t>
+          <t>-1.89%337</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+7.07%</t>
+          <t>-1.89%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>272.5</v>
+        <v>337</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-29 00:03:06</t>
+          <t>2026-10-29 23:20:13</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3371,21 +3371,21 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2049上銀</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+4.57%343.5</t>
+          <t>-9.77%115.5</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+4.57%</t>
+          <t>-9.77%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>343.5</v>
+        <v>115.5</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-29 00:03:06</t>
+          <t>2026-10-29 23:20:13</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,16 +3437,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>+4.09%2035</t>
+          <t>-4.42%1945</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>+4.09%</t>
+          <t>-4.42%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>2035</v>
+        <v>1945</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-29 00:03:06</t>
+          <t>2026-10-29 23:20:13</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+5.52%172</t>
+          <t>-0.87%170.5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+5.52%</t>
+          <t>-0.87%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>172</v>
+        <v>170.5</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>

--- a/etf_holdings/2026-10-29_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-29_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:09</t>
+          <t>2026-10-29 23:33:01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:09</t>
+          <t>2026-10-29 23:33:01</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:09</t>
+          <t>2026-10-29 23:33:01</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:09</t>
+          <t>2026-10-29 23:33:01</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:09</t>
+          <t>2026-10-29 23:33:01</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:09</t>
+          <t>2026-10-29 23:33:01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:09</t>
+          <t>2026-10-29 23:33:01</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:09</t>
+          <t>2026-10-29 23:33:01</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:09</t>
+          <t>2026-10-29 23:33:01</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:09</t>
+          <t>2026-10-29 23:33:01</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:09</t>
+          <t>2026-10-29 23:33:01</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:09</t>
+          <t>2026-10-29 23:33:01</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:09</t>
+          <t>2026-10-29 23:33:01</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:09</t>
+          <t>2026-10-29 23:33:01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:09</t>
+          <t>2026-10-29 23:33:01</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:10</t>
+          <t>2026-10-29 23:33:02</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:10</t>
+          <t>2026-10-29 23:33:02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:10</t>
+          <t>2026-10-29 23:33:02</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:10</t>
+          <t>2026-10-29 23:33:02</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:10</t>
+          <t>2026-10-29 23:33:02</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:10</t>
+          <t>2026-10-29 23:33:02</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:10</t>
+          <t>2026-10-29 23:33:02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:10</t>
+          <t>2026-10-29 23:33:02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:10</t>
+          <t>2026-10-29 23:33:02</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:10</t>
+          <t>2026-10-29 23:33:02</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:10</t>
+          <t>2026-10-29 23:33:02</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:10</t>
+          <t>2026-10-29 23:33:02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:10</t>
+          <t>2026-10-29 23:33:02</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:10</t>
+          <t>2026-10-29 23:33:02</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:10</t>
+          <t>2026-10-29 23:33:02</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:12</t>
+          <t>2026-10-29 23:33:04</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:12</t>
+          <t>2026-10-29 23:33:04</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:12</t>
+          <t>2026-10-29 23:33:04</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:12</t>
+          <t>2026-10-29 23:33:04</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:12</t>
+          <t>2026-10-29 23:33:04</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:12</t>
+          <t>2026-10-29 23:33:04</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:12</t>
+          <t>2026-10-29 23:33:04</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:12</t>
+          <t>2026-10-29 23:33:04</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:12</t>
+          <t>2026-10-29 23:33:04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:12</t>
+          <t>2026-10-29 23:33:04</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:12</t>
+          <t>2026-10-29 23:33:04</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:12</t>
+          <t>2026-10-29 23:33:04</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:12</t>
+          <t>2026-10-29 23:33:04</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:12</t>
+          <t>2026-10-29 23:33:04</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:12</t>
+          <t>2026-10-29 23:33:04</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:13</t>
+          <t>2026-10-29 23:33:05</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:13</t>
+          <t>2026-10-29 23:33:05</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:13</t>
+          <t>2026-10-29 23:33:05</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:13</t>
+          <t>2026-10-29 23:33:05</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:13</t>
+          <t>2026-10-29 23:33:05</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
